--- a/Outputs/Scenarios/PtX_demand_SK_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SK_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001396519609567323</v>
       </c>
       <c r="K16" t="n">
-        <v>3.084607230385784e-05</v>
+        <v>7.197416870900163e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.084607230385786e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6.169214460771569e-05</v>
+        <v>2.467685784308629e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>2.012148366262912e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.028202410128595e-05</v>
+        <v>3.084607230385786e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0020673772607307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001544367736555476</v>
+        <v>0.0003603524718629444</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.544367736555476e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003088735473110952</v>
+        <v>0.0001235494189244381</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001088093295121421</v>
       </c>
       <c r="K42" t="n">
-        <v>5.147892455184921e-05</v>
+        <v>1.544367736555476e-05</v>
       </c>
     </row>
     <row r="43">
